--- a/Databases/Database3BandReview/Winter Birds 2024 Band Review.xlsx
+++ b/Databases/Database3BandReview/Winter Birds 2024 Band Review.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rohanpoudel/Documents/USFWS/PipingPlover/Databases/Database3BandReview/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EEADFF9-BFCE-6B4E-A552-1505C9A4A1F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BF6FEC8-572F-5048-B7AD-C46C84155A12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-19820" yWindow="-28200" windowWidth="34400" windowHeight="28200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Focal Observations" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="148">
   <si>
     <t xml:space="preserve">Transect </t>
   </si>
@@ -417,9 +417,6 @@
   </si>
   <si>
     <t>Pinellas</t>
-  </si>
-  <si>
-    <t>2 banded birds observed but only incomplete band combos recorded</t>
   </si>
   <si>
     <t>Caladesi Island State Park</t>
@@ -2491,9 +2488,7 @@
       <c r="I26">
         <v>25</v>
       </c>
-      <c r="J26" s="1" t="s">
-        <v>130</v>
-      </c>
+      <c r="J26" s="1"/>
       <c r="K26">
         <v>28.156099999999999</v>
       </c>
@@ -2536,7 +2531,7 @@
     </row>
     <row r="27" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B27" t="s">
         <v>129</v>
@@ -2575,7 +2570,7 @@
         <v>16</v>
       </c>
       <c r="N27" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="O27">
         <v>28.050799999999999</v>
@@ -2590,7 +2585,7 @@
         <v>85</v>
       </c>
       <c r="S27" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="T27">
         <v>-82.821899999999999</v>
@@ -2610,7 +2605,7 @@
     </row>
     <row r="28" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B28" t="s">
         <v>129</v>
@@ -2627,7 +2622,7 @@
     </row>
     <row r="29" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B29" t="s">
         <v>129</v>
@@ -2642,12 +2637,12 @@
         <v>11</v>
       </c>
       <c r="F29" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="30" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B30" t="s">
         <v>129</v>
@@ -2685,7 +2680,7 @@
     </row>
     <row r="31" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B31" t="s">
         <v>129</v>
@@ -2765,7 +2760,7 @@
     </row>
     <row r="32" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B32" t="s">
         <v>129</v>
@@ -2788,7 +2783,7 @@
     </row>
     <row r="33" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B33" t="s">
         <v>129</v>
@@ -2803,12 +2798,12 @@
         <v>25</v>
       </c>
       <c r="F33" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="34" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B34" t="s">
         <v>129</v>
@@ -2849,10 +2844,10 @@
     </row>
     <row r="35" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
+        <v>142</v>
+      </c>
+      <c r="B35" t="s">
         <v>143</v>
-      </c>
-      <c r="B35" t="s">
-        <v>144</v>
       </c>
       <c r="C35">
         <v>29.860199999999999</v>
@@ -2893,10 +2888,10 @@
     </row>
     <row r="36" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B36" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C36">
         <v>29.827279999999998</v>
@@ -2943,10 +2938,10 @@
     </row>
     <row r="37" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
+        <v>145</v>
+      </c>
+      <c r="B37" t="s">
         <v>146</v>
-      </c>
-      <c r="B37" t="s">
-        <v>147</v>
       </c>
       <c r="C37">
         <v>29.067550000000001</v>
@@ -2976,7 +2971,7 @@
         <v>30</v>
       </c>
       <c r="R37" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
   </sheetData>
